--- a/artfynd/A 27307-2026 artfynd.xlsx
+++ b/artfynd/A 27307-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>128012</v>
       </c>
       <c r="B2" t="n">
-        <v>90595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514278.8015349256</v>
+        <v>514279</v>
       </c>
       <c r="R2" t="n">
-        <v>6237541.708839231</v>
+        <v>6237542</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2009-03-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-03-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>14119970</v>
       </c>
       <c r="B3" t="n">
-        <v>9310</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514271.2065269715</v>
+        <v>514271</v>
       </c>
       <c r="R3" t="n">
-        <v>6237484.516143339</v>
+        <v>6237485</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -898,19 +878,9 @@
           <t>2009-06-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
